--- a/files/scripts/statistical_test_scripts/rq3_result/rq3_paired_edge_vs_event.xlsx
+++ b/files/scripts/statistical_test_scripts/rq3_result/rq3_paired_edge_vs_event.xlsx
@@ -695,32 +695,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -968,7 +964,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>9.5367431640625e-07</v>
+        <v>6.103515625e-07</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1018,7 +1014,7 @@
         <v>2.67277858553444e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>9.503212748566899e-05</v>
+        <v>6.335475165711267e-05</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1068,7 +1064,7 @@
         <v>2.571042765083602e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>9.503212748566899e-05</v>
+        <v>6.328720652513482e-05</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1103,28 +1099,28 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>78.95</v>
+        <v>58.82</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>21.05</v>
+        <v>9.409999999999997</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0006402330973173942</v>
+        <v>0.002415657043457031</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002095866698834225</v>
+        <v>0.005153401692708334</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1276,7 +1272,7 @@
         <v>0.0006549583433856954</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002095866698834225</v>
+        <v>0.001497047642024447</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -1380,7 +1376,7 @@
         <v>0.001886167459244937</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005748319875794093</v>
+        <v>0.00416257646178193</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -1526,25 +1522,25 @@
         <v>30.215</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>69.785</v>
+        <v>18.685</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.579979122000136e-08</v>
+        <v>2.130824600258387e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>6.741244253867249e-08</v>
+        <v>5.682198934022366e-08</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.9846938775510204</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1804,7 +1800,7 @@
         <v>1.631856382480309e-13</v>
       </c>
       <c r="I26" t="n">
-        <v>8.033754498364599e-13</v>
+        <v>4.540817759945208e-13</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -1854,7 +1850,7 @@
         <v>1.631856382480309e-13</v>
       </c>
       <c r="I27" t="n">
-        <v>8.033754498364599e-13</v>
+        <v>4.540817759945208e-13</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -1904,7 +1900,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="I28" t="n">
-        <v>8.033754498364599e-13</v>
+        <v>4.540817759945208e-13</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1939,37 +1935,37 @@
         <v>498</v>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>28.57</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-61.11</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.290412233220229e-09</v>
+        <v>2.667751802518537e-83</v>
       </c>
       <c r="I29" t="n">
-        <v>1.047045592329247e-08</v>
+        <v>3.414722307223728e-82</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5471887550200804</v>
+        <v>0</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2112,7 +2108,7 @@
         <v>1.413734078775842e-72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.809579620833078e-71</v>
+        <v>1.507983017360898e-71</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -2351,13 +2347,13 @@
         <v>2664</v>
       </c>
       <c r="D37" t="n">
-        <v>74.51000000000001</v>
+        <v>55.22</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>25.48999999999999</v>
+        <v>-35.41</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2372,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9679054054054054</v>
+        <v>0.001372571896220545</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2381,7 +2377,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2617,44 +2613,40 @@
         <v>400</v>
       </c>
       <c r="D42" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.410000000000011</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>1.53271882463032e-44</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>6.130875298521281e-44</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5</v>
+        <v>0.626921875</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2671,44 +2663,40 @@
         <v>400</v>
       </c>
       <c r="D43" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.410000000000011</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>1.53271882463032e-44</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>6.130875298521281e-44</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>0.626921875</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2725,44 +2713,40 @@
         <v>400</v>
       </c>
       <c r="D44" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="E44" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1.410000000000011</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>1.53271882463032e-44</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>6.130875298521281e-44</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>0.626921875</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2779,28 +2763,28 @@
         <v>400</v>
       </c>
       <c r="D45" t="n">
-        <v>87.88</v>
+        <v>24.32</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>12.12</v>
+        <v>73.33</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4.553510854438712e-63</v>
+        <v>2.615604615355988e-67</v>
       </c>
       <c r="I45" t="n">
-        <v>4.163209924058251e-62</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9675</v>
+        <v>0.99923125</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3003,16 +2987,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3173105078629141</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9230851137830229</v>
+        <v>1</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.50125</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3021,10 +3005,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>all ties</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3056,7 +3044,7 @@
         <v>2.387238385100547e-67</v>
       </c>
       <c r="I50" t="n">
-        <v>2.546387610773917e-66</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
@@ -3091,44 +3079,40 @@
         <v>400</v>
       </c>
       <c r="D51" t="n">
-        <v>100</v>
+        <v>6.78</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9.280000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>2.386531685205457e-67</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3145,44 +3129,40 @@
         <v>400</v>
       </c>
       <c r="D52" t="n">
-        <v>100</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>10.84</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3199,44 +3179,40 @@
         <v>400</v>
       </c>
       <c r="D53" t="n">
-        <v>100</v>
+        <v>14.34</v>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>5.26</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-9.169999999999998</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2.720288863135073e-67</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3415,44 +3391,40 @@
         <v>400</v>
       </c>
       <c r="D57" t="n">
-        <v>100</v>
+        <v>83.88</v>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>10.83</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.339219132620344e-66</v>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5</v>
+        <v>0.90934375</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3469,7 +3441,7 @@
         <v>416</v>
       </c>
       <c r="D58" t="n">
-        <v>40.28</v>
+        <v>36.76</v>
       </c>
       <c r="E58" t="n">
         <v>33.33</v>
@@ -3478,19 +3450,19 @@
         <v>-3.43</v>
       </c>
       <c r="G58" t="n">
-        <v>162</v>
+        <v>17148</v>
       </c>
       <c r="H58" t="n">
-        <v>4.983831804176331e-58</v>
+        <v>6.093904981971648e-27</v>
       </c>
       <c r="I58" t="n">
-        <v>3.189652354672852e-57</v>
+        <v>1.950049594230927e-26</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2357156065088757</v>
+        <v>0.2524038461538461</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3519,7 +3491,7 @@
         <v>416</v>
       </c>
       <c r="D59" t="n">
-        <v>41.67</v>
+        <v>38.24</v>
       </c>
       <c r="E59" t="n">
         <v>35</v>
@@ -3528,19 +3500,19 @@
         <v>-3.240000000000002</v>
       </c>
       <c r="G59" t="n">
-        <v>162</v>
+        <v>17148</v>
       </c>
       <c r="H59" t="n">
-        <v>4.983831804176331e-58</v>
+        <v>6.093904981971648e-27</v>
       </c>
       <c r="I59" t="n">
-        <v>3.189652354672852e-57</v>
+        <v>1.950049594230927e-26</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2357156065088757</v>
+        <v>0.2524038461538461</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3569,7 +3541,7 @@
         <v>416</v>
       </c>
       <c r="D60" t="n">
-        <v>43.06</v>
+        <v>39.71</v>
       </c>
       <c r="E60" t="n">
         <v>36.67</v>
@@ -3578,19 +3550,19 @@
         <v>-3.039999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>162</v>
+        <v>17148</v>
       </c>
       <c r="H60" t="n">
-        <v>4.983831804176331e-58</v>
+        <v>6.093904981971648e-27</v>
       </c>
       <c r="I60" t="n">
-        <v>3.189652354672852e-57</v>
+        <v>1.950049594230927e-26</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2357156065088757</v>
+        <v>0.2524038461538461</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3619,44 +3591,40 @@
         <v>416</v>
       </c>
       <c r="D61" t="n">
-        <v>100</v>
+        <v>56.72</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>9.379999999999995</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.155770802073705e-70</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3835,44 +3803,40 @@
         <v>416</v>
       </c>
       <c r="D65" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="E65" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.8400000000000034</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3.00941509314706e-42</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.132956270361246e-41</v>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>0.658203125</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3994,10 +3958,10 @@
         <v>31.745</v>
       </c>
       <c r="E2" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.57</v>
+        <v>-5.549999999999997</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4006,13 +3970,13 @@
         <v>0.00048828125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2534722222222222</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4041,13 +4005,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>38.395</v>
+        <v>36.05</v>
       </c>
       <c r="E3" t="n">
         <v>31.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.06</v>
+        <v>-7.064999999999998</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4056,13 +4020,13 @@
         <v>0.00048828125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.34375</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4106,17 +4070,17 @@
         <v>0.00048828125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.34375</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -4141,13 +4105,13 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>58.115</v>
+        <v>60.715</v>
       </c>
       <c r="E5" t="n">
         <v>47.725</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.150000000000002</v>
+        <v>-8.020000000000003</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4156,13 +4120,13 @@
         <v>0.00048828125</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2013888888888889</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -4206,7 +4170,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -4256,7 +4220,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -4306,7 +4270,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -4356,7 +4320,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -4403,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.692924356525407e-05</v>
+        <v>2.695812077387092e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>4.797692872831902e-05</v>
+        <v>3.750695064190737e-05</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -4441,28 +4405,28 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>60.34</v>
+        <v>62.07</v>
       </c>
       <c r="E11" t="n">
         <v>26.92</v>
       </c>
       <c r="F11" t="n">
-        <v>-31.25</v>
+        <v>-36.21</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.698702240967945e-05</v>
+        <v>2.695812077387092e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>4.797692872831902e-05</v>
+        <v>3.750695064190737e-05</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05482041587901702</v>
+        <v>0.04536862003780719</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -4494,25 +4458,25 @@
         <v>24.62</v>
       </c>
       <c r="E12" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.16</v>
+        <v>-12.15</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>5.960464477539062e-06</v>
+        <v>4.529953002929688e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>1.155968868371212e-05</v>
+        <v>6.90278552827381e-06</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1398865784499055</v>
+        <v>0.1512287334593573</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -4541,28 +4505,28 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>76.19</v>
       </c>
       <c r="E13" t="n">
-        <v>47.92</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.18000000000001</v>
+        <v>-38.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.384185791015625e-07</v>
+        <v>3.337860107421875e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>4.76837158203125e-07</v>
+        <v>5.210318216463415e-06</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0113421550094518</v>
+        <v>0.04158790170132325</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -4591,13 +4555,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>54.55</v>
+        <v>54.35</v>
       </c>
       <c r="E14" t="n">
         <v>26.79</v>
       </c>
       <c r="F14" t="n">
-        <v>-28.57</v>
+        <v>-27.58</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4606,7 +4570,7 @@
         <v>2.695812077387092e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>4.797692872831902e-05</v>
+        <v>3.750695064190737e-05</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -4656,7 +4620,7 @@
         <v>0.0004270857672052102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0006793478260869565</v>
+        <v>0.0005681818181818182</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -4706,10 +4670,10 @@
         <v>0.04380372353657391</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0572130266600149</v>
+        <v>0.04918312818141633</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0.6077504725897921</v>
@@ -4741,28 +4705,28 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>24.12</v>
+        <v>27.42</v>
       </c>
       <c r="E17" t="n">
-        <v>15.38</v>
+        <v>16.98</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.509999999999998</v>
+        <v>-7.25</v>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0001277923583984375</v>
+        <v>4.76837158203125e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000221046241554054</v>
+        <v>7.62939453125e-07</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2041587901701323</v>
+        <v>0.2325141776937618</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -4797,16 +4761,16 @@
         <v>12.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-36.495</v>
+        <v>-37.61499999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.645823956448885e-08</v>
+        <v>1.646351855095233e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -4844,7 +4808,7 @@
         <v>14.09</v>
       </c>
       <c r="E19" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="F19" t="n">
         <v>-9.959999999999999</v>
@@ -4853,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.644768605898686e-08</v>
+        <v>1.645296206728656e-08</v>
       </c>
       <c r="I19" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -4894,19 +4858,19 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.67</v>
+        <v>-7.74</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.646879902703648e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>1.212659602363904e-12</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -4944,25 +4908,25 @@
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>52.44</v>
       </c>
       <c r="F21" t="n">
-        <v>-50</v>
+        <v>-47.56</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.180054699024209e-08</v>
+        <v>1.220145455994324e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>3.020940029501974e-08</v>
+        <v>1.816030446131087e-05</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -4991,22 +4955,22 @@
         <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>48.96</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
         <v>17.14</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.07</v>
+        <v>-29.08</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.594293398555841e-08</v>
+        <v>1.622743344620094e-08</v>
       </c>
       <c r="I22" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -5056,7 +5020,7 @@
         <v>1.594293398555841e-08</v>
       </c>
       <c r="I23" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -5106,7 +5070,7 @@
         <v>1.59480672652879e-08</v>
       </c>
       <c r="I24" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -5141,28 +5105,28 @@
         <v>42</v>
       </c>
       <c r="D25" t="n">
-        <v>18.35</v>
+        <v>22.665</v>
       </c>
       <c r="E25" t="n">
-        <v>5.145</v>
+        <v>6.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.87</v>
+        <v>-14.565</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.646879902703648e-08</v>
+        <v>1.647408099309982e-08</v>
       </c>
       <c r="I25" t="n">
-        <v>3.400010121710756e-08</v>
+        <v>2.703438932200996e-08</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.008503401360544218</v>
+        <v>0.0300453514739229</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -5191,28 +5155,28 @@
         <v>498</v>
       </c>
       <c r="D26" t="n">
-        <v>35.56</v>
+        <v>35.33</v>
       </c>
       <c r="E26" t="n">
-        <v>31.48</v>
+        <v>31.465</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.625</v>
+        <v>-3.49</v>
       </c>
       <c r="G26" t="n">
-        <v>4466</v>
+        <v>4534</v>
       </c>
       <c r="H26" t="n">
-        <v>6.902216913865615e-66</v>
+        <v>1.032976597229625e-65</v>
       </c>
       <c r="I26" t="n">
-        <v>3.155299160624281e-65</v>
+        <v>2.542711623949845e-65</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3094687988903405</v>
+        <v>0.3085131691424332</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -5241,32 +5205,32 @@
         <v>498</v>
       </c>
       <c r="D27" t="n">
-        <v>38.46</v>
+        <v>38.615</v>
       </c>
       <c r="E27" t="n">
-        <v>34.33</v>
+        <v>34.48</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.305</v>
+        <v>-3.449999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>7546</v>
+        <v>7065</v>
       </c>
       <c r="H27" t="n">
-        <v>2.13989629516425e-57</v>
+        <v>9.038502057062653e-59</v>
       </c>
       <c r="I27" t="n">
-        <v>7.608520160584001e-57</v>
+        <v>2.142459746859296e-58</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3643792035612329</v>
+        <v>0.3590063063498976</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5291,28 +5255,28 @@
         <v>498</v>
       </c>
       <c r="D28" t="n">
-        <v>41.41500000000001</v>
+        <v>41.325</v>
       </c>
       <c r="E28" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.195000000000002</v>
+        <v>-3.23</v>
       </c>
       <c r="G28" t="n">
-        <v>3899</v>
+        <v>2642</v>
       </c>
       <c r="H28" t="n">
-        <v>2.340201195852544e-67</v>
+        <v>7.491782464833543e-71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.333130531022628e-66</v>
+        <v>2.996712985933417e-70</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3703266882792213</v>
+        <v>0.3667198916146513</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -5341,28 +5305,28 @@
         <v>498</v>
       </c>
       <c r="D29" t="n">
-        <v>51.3</v>
+        <v>46.97</v>
       </c>
       <c r="E29" t="n">
-        <v>40.38</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>-10</v>
+        <v>53.03</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H29" t="n">
-        <v>2.625274707410627e-83</v>
+        <v>7.904914816684674e-83</v>
       </c>
       <c r="I29" t="n">
-        <v>1.687480373057312e-82</v>
+        <v>5.059145482678192e-82</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.03554579764842503</v>
+        <v>0.9753592683988968</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -5371,7 +5335,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -5403,16 +5367,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.63668808290205e-83</v>
+        <v>2.634534250076414e-83</v>
       </c>
       <c r="I30" t="n">
-        <v>1.687480373057312e-82</v>
+        <v>1.873446577832117e-82</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07477500362897373</v>
+        <v>0.07363187690521121</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -5456,7 +5420,7 @@
         <v>3.127476806111664e-36</v>
       </c>
       <c r="I31" t="n">
-        <v>8.702544156136805e-36</v>
+        <v>6.254953612223329e-36</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -5506,10 +5470,10 @@
         <v>0.03896170592257132</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0519489412300951</v>
+        <v>0.04452766391151008</v>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0.5356728117288431</v>
@@ -5541,28 +5505,28 @@
         <v>498</v>
       </c>
       <c r="D33" t="n">
-        <v>46.955</v>
+        <v>47.22</v>
       </c>
       <c r="E33" t="n">
-        <v>44.095</v>
+        <v>44.12</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.130000000000003</v>
+        <v>-3.045000000000002</v>
       </c>
       <c r="G33" t="n">
-        <v>11618.5</v>
+        <v>11399.5</v>
       </c>
       <c r="H33" t="n">
-        <v>5.512450243726234e-49</v>
+        <v>1.259471353397978e-48</v>
       </c>
       <c r="I33" t="n">
-        <v>1.620817955293249e-48</v>
+        <v>2.600198923144212e-48</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3430388219544846</v>
+        <v>0.3425065724746375</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -5591,13 +5555,13 @@
         <v>2664</v>
       </c>
       <c r="D34" t="n">
-        <v>60.065</v>
+        <v>60.5</v>
       </c>
       <c r="E34" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="F34" t="n">
-        <v>-31.47</v>
+        <v>-31.42</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -5612,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.01550980879528177</v>
+        <v>0.01618144044945847</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -5641,16 +5605,16 @@
         <v>2664</v>
       </c>
       <c r="D35" t="n">
-        <v>31.39</v>
+        <v>31.45</v>
       </c>
       <c r="E35" t="n">
-        <v>18.475</v>
+        <v>18.415</v>
       </c>
       <c r="F35" t="n">
-        <v>-11.9</v>
+        <v>-11.99</v>
       </c>
       <c r="G35" t="n">
-        <v>3011</v>
+        <v>2740</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -5662,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02207190298406515</v>
+        <v>0.02109866059753447</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -5691,13 +5655,13 @@
         <v>2664</v>
       </c>
       <c r="D36" t="n">
-        <v>22.19</v>
+        <v>22.3</v>
       </c>
       <c r="E36" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="F36" t="n">
-        <v>-7.930000000000001</v>
+        <v>-8.004999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -5712,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.05075895151908665</v>
+        <v>0.05231526571616662</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -5741,16 +5705,16 @@
         <v>2664</v>
       </c>
       <c r="D37" t="n">
-        <v>60.53</v>
+        <v>67.465</v>
       </c>
       <c r="E37" t="n">
-        <v>34.78</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>-24.99999999999999</v>
+        <v>32.43000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -5762,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0599314827214602</v>
+        <v>0.8551759811613415</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -5771,7 +5735,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5794,10 +5758,10 @@
         <v>39.34</v>
       </c>
       <c r="E38" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="F38" t="n">
-        <v>-15.135</v>
+        <v>-15.2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -5812,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00346609278197116</v>
+        <v>0.003578113586559533</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5841,13 +5805,13 @@
         <v>2664</v>
       </c>
       <c r="D39" t="n">
-        <v>22.78</v>
+        <v>22.73</v>
       </c>
       <c r="E39" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="F39" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -5862,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01346828247166085</v>
+        <v>0.01358136007629251</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5891,13 +5855,13 @@
         <v>2664</v>
       </c>
       <c r="D40" t="n">
-        <v>14.04</v>
+        <v>14.05</v>
       </c>
       <c r="E40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.109999999999998</v>
+        <v>-5.150000000000002</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5912,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.08561059651994336</v>
+        <v>0.08601626682989295</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5941,16 +5905,16 @@
         <v>2664</v>
       </c>
       <c r="D41" t="n">
-        <v>21.68</v>
+        <v>22.345</v>
       </c>
       <c r="E41" t="n">
-        <v>15.08</v>
+        <v>16.34</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.09</v>
+        <v>-5.18</v>
       </c>
       <c r="G41" t="n">
-        <v>3403.5</v>
+        <v>2599</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -5962,7 +5926,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1754104188648108</v>
+        <v>0.2017315034629224</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -5991,10 +5955,10 @@
         <v>400</v>
       </c>
       <c r="D42" t="n">
-        <v>6.77</v>
+        <v>12.3</v>
       </c>
       <c r="E42" t="n">
-        <v>3.92</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="F42" t="n">
         <v>-0.8700000000000001</v>
@@ -6003,16 +5967,16 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>5.552113587156062e-49</v>
+        <v>5.551548136542687e-49</v>
       </c>
       <c r="I42" t="n">
-        <v>1.620817955293249e-48</v>
+        <v>1.187575375067631e-48</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.37634375</v>
+        <v>0.374940625</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -6041,32 +6005,32 @@
         <v>400</v>
       </c>
       <c r="D43" t="n">
-        <v>5.68</v>
+        <v>9.649999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>3.55</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.7249999999999996</v>
+        <v>-0.71</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.821113643886472e-49</v>
+        <v>3.816067098322758e-49</v>
       </c>
       <c r="I43" t="n">
-        <v>1.287111964256496e-48</v>
+        <v>8.722439081880589e-49</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.357740625</v>
+        <v>0.368575</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6091,10 +6055,10 @@
         <v>400</v>
       </c>
       <c r="D44" t="n">
-        <v>4.885</v>
+        <v>7.925000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>2.71</v>
+        <v>4.225</v>
       </c>
       <c r="F44" t="n">
         <v>-0.63</v>
@@ -6103,16 +6067,16 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.571561721320545e-49</v>
+        <v>5.566759570629518e-49</v>
       </c>
       <c r="I44" t="n">
-        <v>1.620817955293249e-48</v>
+        <v>1.187575375067631e-48</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.32493125</v>
+        <v>0.34063125</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6141,28 +6105,28 @@
         <v>400</v>
       </c>
       <c r="D45" t="n">
-        <v>23.11</v>
+        <v>100</v>
       </c>
       <c r="E45" t="n">
-        <v>18.59</v>
+        <v>21.74</v>
       </c>
       <c r="F45" t="n">
-        <v>-5.060000000000002</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.578908895994553e-67</v>
+        <v>2.438246141839461e-67</v>
       </c>
       <c r="I45" t="n">
-        <v>1.333130531022628e-66</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.25179375</v>
+        <v>0</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -6191,10 +6155,10 @@
         <v>400</v>
       </c>
       <c r="D46" t="n">
-        <v>11.39</v>
+        <v>11.95</v>
       </c>
       <c r="E46" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="F46" t="n">
         <v>-2.52</v>
@@ -6203,16 +6167,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>7.481966671161719e-63</v>
+        <v>1.939615901792861e-67</v>
       </c>
       <c r="I46" t="n">
-        <v>2.821994308948888e-62</v>
+        <v>6.54793746564941e-67</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3565875</v>
+        <v>0.33471875</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6241,28 +6205,28 @@
         <v>400</v>
       </c>
       <c r="D47" t="n">
-        <v>8.49</v>
+        <v>8.74</v>
       </c>
       <c r="E47" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.72</v>
+        <v>-1.88</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7.495922383145484e-63</v>
+        <v>1.943918935114669e-67</v>
       </c>
       <c r="I47" t="n">
-        <v>2.821994308948888e-62</v>
+        <v>6.54793746564941e-67</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0.39510625</v>
+        <v>0.3792125</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6291,28 +6255,28 @@
         <v>400</v>
       </c>
       <c r="D48" t="n">
-        <v>8.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.65</v>
+        <v>-1.7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>7.495432274927977e-63</v>
+        <v>1.943809011806541e-67</v>
       </c>
       <c r="I48" t="n">
-        <v>2.821994308948888e-62</v>
+        <v>6.54793746564941e-67</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.400425</v>
+        <v>0.3874125</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -6341,28 +6305,28 @@
         <v>400</v>
       </c>
       <c r="D49" t="n">
-        <v>6.075</v>
+        <v>5.785</v>
       </c>
       <c r="E49" t="n">
-        <v>4.67</v>
+        <v>4.32</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.707921391139714e-67</v>
+        <v>2.689109776691231e-67</v>
       </c>
       <c r="I49" t="n">
-        <v>1.333130531022628e-66</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3917125</v>
+        <v>0.3908375</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -6445,10 +6409,10 @@
         <v>400</v>
       </c>
       <c r="D51" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="E51" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -6499,10 +6463,10 @@
         <v>400</v>
       </c>
       <c r="D52" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="E52" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6553,10 +6517,10 @@
         <v>400</v>
       </c>
       <c r="D53" t="n">
-        <v>6.72</v>
+        <v>100</v>
       </c>
       <c r="E53" t="n">
-        <v>6.72</v>
+        <v>100</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -6607,44 +6571,40 @@
         <v>400</v>
       </c>
       <c r="D54" t="n">
-        <v>2.005</v>
+        <v>33.44</v>
       </c>
       <c r="E54" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-19.78</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2.727457768070496e-67</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6661,44 +6621,40 @@
         <v>400</v>
       </c>
       <c r="D55" t="n">
-        <v>2.4</v>
+        <v>31.395</v>
       </c>
       <c r="E55" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-16.995</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2.728235197751723e-67</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6715,44 +6671,40 @@
         <v>400</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>29.015</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-15.29</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>2.729377744142024e-67</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6769,32 +6721,32 @@
         <v>400</v>
       </c>
       <c r="D57" t="n">
-        <v>0.28</v>
+        <v>11.9</v>
       </c>
       <c r="E57" t="n">
-        <v>0.28</v>
+        <v>1.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-10.47</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0006549583433856954</v>
+        <v>2.690955763825766e-67</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0008918581697166916</v>
+        <v>6.987207025003583e-67</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0.49861875</v>
+        <v>0</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6981,44 +6933,40 @@
         <v>416</v>
       </c>
       <c r="D61" t="n">
-        <v>20.49</v>
+        <v>44.38</v>
       </c>
       <c r="E61" t="n">
-        <v>20.49</v>
+        <v>21.03</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-23.35</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7035,44 +6983,40 @@
         <v>416</v>
       </c>
       <c r="D62" t="n">
-        <v>5.57</v>
+        <v>11.41</v>
       </c>
       <c r="E62" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7089,44 +7033,40 @@
         <v>416</v>
       </c>
       <c r="D63" t="n">
-        <v>3.65</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>-1.239999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7143,44 +7083,40 @@
         <v>416</v>
       </c>
       <c r="D64" t="n">
-        <v>3.21</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-1.239999999999999</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7197,44 +7133,40 @@
         <v>416</v>
       </c>
       <c r="D65" t="n">
-        <v>2.58</v>
+        <v>5.66</v>
       </c>
       <c r="E65" t="n">
-        <v>2.58</v>
+        <v>4.85</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-0.8399999999999999</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3.029989884439326e-71</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.292795684027446e-70</v>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>0.2970945821005917</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7356,10 +7288,10 @@
         <v>31.745</v>
       </c>
       <c r="E2" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.57</v>
+        <v>-5.549999999999997</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -7368,13 +7300,13 @@
         <v>0.00048828125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2534722222222222</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -7403,13 +7335,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>38.395</v>
+        <v>36.05</v>
       </c>
       <c r="E3" t="n">
         <v>31.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.06</v>
+        <v>-7.064999999999998</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7418,13 +7350,13 @@
         <v>0.00048828125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.34375</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -7468,17 +7400,17 @@
         <v>0.00048828125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.34375</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -7503,32 +7435,32 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>58.115</v>
+        <v>53.57</v>
       </c>
       <c r="E5" t="n">
         <v>47.725</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.150000000000002</v>
+        <v>-5.949999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00048828125</v>
+        <v>0.12353515625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.1254960317460317</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.4027777777777778</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -7568,7 +7500,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -7618,7 +7550,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -7668,7 +7600,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -7718,7 +7650,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005122950819672131</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -7768,13 +7700,13 @@
         <v>8.152026989406104e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001410080344113488</v>
+        <v>0.0001003326398696136</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1862003780718336</v>
+        <v>0.1899810964083176</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -7803,28 +7735,28 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>44.83</v>
+        <v>46.55</v>
       </c>
       <c r="E11" t="n">
         <v>25.86</v>
       </c>
       <c r="F11" t="n">
-        <v>-16.18</v>
+        <v>-17.14</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0005517005920410156</v>
+        <v>0.0002534389495849609</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000720588528380102</v>
+        <v>0.0003060394862912736</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1824196597353497</v>
+        <v>0.1587901701323251</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -7853,28 +7785,28 @@
         <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>19.38</v>
+        <v>19.09</v>
       </c>
       <c r="E12" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.260000000000002</v>
+        <v>-5.840000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08582782745361328</v>
+        <v>0.0448758602142334</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1056342491736779</v>
+        <v>0.04632346860824093</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2703213610586012</v>
+        <v>0.2419659735349717</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -7903,28 +7835,28 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>39.47</v>
       </c>
       <c r="E13" t="n">
-        <v>47.92</v>
+        <v>20.97</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.559999999999995</v>
+        <v>-22.6</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005733990950307122</v>
+        <v>2.384185791015625e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007195596486659918</v>
+        <v>3.114038584183673e-07</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2731568998109641</v>
+        <v>0.0945179584120983</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -7953,13 +7885,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>54.55</v>
+        <v>54.35</v>
       </c>
       <c r="E14" t="n">
         <v>26.79</v>
       </c>
       <c r="F14" t="n">
-        <v>-28.57</v>
+        <v>-27.58</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -7968,7 +7900,7 @@
         <v>2.695812077387092e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>4.792554804243719e-05</v>
+        <v>3.382979861819096e-05</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -8018,7 +7950,7 @@
         <v>0.0004270857672052102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0005061757240950639</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -8068,7 +8000,7 @@
         <v>0.6142712680950519</v>
       </c>
       <c r="I16" t="n">
-        <v>0.741761531284591</v>
+        <v>0.6142712680950519</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -8103,28 +8035,28 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>24.12</v>
+        <v>27.42</v>
       </c>
       <c r="E17" t="n">
-        <v>15.38</v>
+        <v>16.98</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.509999999999998</v>
+        <v>-7.25</v>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0001277923583984375</v>
+        <v>4.76837158203125e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0002152292351973684</v>
+        <v>6.103515625e-07</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2041587901701323</v>
+        <v>0.2325141776937618</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -8153,13 +8085,13 @@
         <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>48.98</v>
+        <v>48.12</v>
       </c>
       <c r="E18" t="n">
         <v>12.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-34.715</v>
+        <v>-35.16</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8168,7 +8100,7 @@
         <v>1.645823956448885e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -8206,7 +8138,7 @@
         <v>14.09</v>
       </c>
       <c r="E19" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="F19" t="n">
         <v>-9.959999999999999</v>
@@ -8215,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.644768605898686e-08</v>
+        <v>1.645296206728656e-08</v>
       </c>
       <c r="I19" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -8256,19 +8188,19 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.67</v>
+        <v>-7.74</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.646879902703648e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>1.003580360577024e-12</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -8306,25 +8238,25 @@
         <v>53.85</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>1.94</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.059999999999999</v>
+        <v>-52.21</v>
       </c>
       <c r="G21" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0001342100899214274</v>
+        <v>1.640553155002977e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0002202421988454194</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2670068027210885</v>
+        <v>0</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -8353,22 +8285,22 @@
         <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>48.96</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
         <v>17.14</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.07</v>
+        <v>-29.08</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.594293398555841e-08</v>
+        <v>1.622743344620094e-08</v>
       </c>
       <c r="I22" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -8418,7 +8350,7 @@
         <v>1.594293398555841e-08</v>
       </c>
       <c r="I23" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -8468,7 +8400,7 @@
         <v>1.59480672652879e-08</v>
       </c>
       <c r="I24" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -8503,28 +8435,28 @@
         <v>42</v>
       </c>
       <c r="D25" t="n">
-        <v>18.35</v>
+        <v>22.665</v>
       </c>
       <c r="E25" t="n">
-        <v>5.145</v>
+        <v>6.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.87</v>
+        <v>-14.565</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.646879902703648e-08</v>
+        <v>1.647408099309982e-08</v>
       </c>
       <c r="I25" t="n">
-        <v>3.011437536372384e-08</v>
+        <v>2.196544132413309e-08</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.008503401360544218</v>
+        <v>0.0300453514739229</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -8553,28 +8485,28 @@
         <v>498</v>
       </c>
       <c r="D26" t="n">
-        <v>35.26</v>
+        <v>34.90000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>31.33</v>
+        <v>31.105</v>
       </c>
       <c r="F26" t="n">
         <v>-2.630000000000003</v>
       </c>
       <c r="G26" t="n">
-        <v>5874</v>
+        <v>6023</v>
       </c>
       <c r="H26" t="n">
-        <v>2.11343239146646e-59</v>
+        <v>5.091356817290542e-59</v>
       </c>
       <c r="I26" t="n">
-        <v>7.956451356109025e-59</v>
+        <v>1.086156121021982e-58</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3069023080272899</v>
+        <v>0.308118014225577</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -8603,28 +8535,28 @@
         <v>498</v>
       </c>
       <c r="D27" t="n">
-        <v>37.77</v>
+        <v>37.78</v>
       </c>
       <c r="E27" t="n">
-        <v>34.045</v>
+        <v>34.33</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.540000000000001</v>
+        <v>-2.640000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>8373</v>
+        <v>7933</v>
       </c>
       <c r="H27" t="n">
-        <v>1.583617946293987e-51</v>
+        <v>8.159437331428011e-53</v>
       </c>
       <c r="I27" t="n">
-        <v>4.606888571037055e-51</v>
+        <v>1.411362133003764e-52</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3852780600312898</v>
+        <v>0.3806632151094337</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -8656,25 +8588,25 @@
         <v>40.91</v>
       </c>
       <c r="E28" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="F28" t="n">
         <v>-2.769999999999996</v>
       </c>
       <c r="G28" t="n">
-        <v>6482</v>
+        <v>5300</v>
       </c>
       <c r="H28" t="n">
-        <v>4.621924133621401e-57</v>
+        <v>2.624744128829232e-60</v>
       </c>
       <c r="I28" t="n">
-        <v>1.408586402627475e-56</v>
+        <v>5.792538767071408e-60</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3874231867227948</v>
+        <v>0.38386276027806</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -8703,28 +8635,28 @@
         <v>498</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="E29" t="n">
-        <v>40.38</v>
+        <v>2.07</v>
       </c>
       <c r="F29" t="n">
-        <v>-10</v>
+        <v>-40.39</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.629628823843095e-83</v>
+        <v>2.678381139366754e-83</v>
       </c>
       <c r="I29" t="n">
-        <v>1.687480373057312e-82</v>
+        <v>1.714163929194723e-82</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0390034031709166</v>
+        <v>0</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -8765,16 +8697,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.63668808290205e-83</v>
+        <v>2.634534250076414e-83</v>
       </c>
       <c r="I30" t="n">
-        <v>1.687480373057312e-82</v>
+        <v>1.714163929194723e-82</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07477500362897373</v>
+        <v>0.07363187690521121</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -8818,7 +8750,7 @@
         <v>3.127476806111664e-36</v>
       </c>
       <c r="I31" t="n">
-        <v>7.413278355227648e-36</v>
+        <v>5.132269630542218e-36</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -8868,7 +8800,7 @@
         <v>1.311051598470228e-13</v>
       </c>
       <c r="I32" t="n">
-        <v>2.99668936793195e-13</v>
+        <v>2.097682557552365e-13</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -8903,28 +8835,28 @@
         <v>498</v>
       </c>
       <c r="D33" t="n">
-        <v>46.955</v>
+        <v>47.22</v>
       </c>
       <c r="E33" t="n">
-        <v>44.095</v>
+        <v>44.12</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.130000000000003</v>
+        <v>-3.045000000000002</v>
       </c>
       <c r="G33" t="n">
-        <v>11618.5</v>
+        <v>11399.5</v>
       </c>
       <c r="H33" t="n">
-        <v>5.512450243726234e-49</v>
+        <v>1.259471353397978e-48</v>
       </c>
       <c r="I33" t="n">
-        <v>1.371461346786596e-48</v>
+        <v>2.121214910986068e-48</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3430388219544846</v>
+        <v>0.3425065724746375</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -8953,16 +8885,16 @@
         <v>2664</v>
       </c>
       <c r="D34" t="n">
-        <v>28.32</v>
+        <v>28.3</v>
       </c>
       <c r="E34" t="n">
-        <v>25.44</v>
+        <v>25.405</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.675000000000001</v>
+        <v>-2.649999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>19262.5</v>
+        <v>24634.5</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8974,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.246691511331151</v>
+        <v>0.2487544554689825</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -9003,16 +8935,16 @@
         <v>2664</v>
       </c>
       <c r="D35" t="n">
-        <v>24.415</v>
+        <v>24.46</v>
       </c>
       <c r="E35" t="n">
-        <v>18.075</v>
+        <v>17.98</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.295000000000002</v>
+        <v>-6.285</v>
       </c>
       <c r="G35" t="n">
-        <v>20742</v>
+        <v>19265</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -9024,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.08131836791746702</v>
+        <v>0.08102147755863973</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -9053,16 +8985,16 @@
         <v>2664</v>
       </c>
       <c r="D36" t="n">
-        <v>18.225</v>
+        <v>18.215</v>
       </c>
       <c r="E36" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="F36" t="n">
         <v>-3.75</v>
       </c>
       <c r="G36" t="n">
-        <v>6712</v>
+        <v>5138</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -9074,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1786580358511665</v>
+        <v>0.1804187351766181</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -9103,13 +9035,13 @@
         <v>2664</v>
       </c>
       <c r="D37" t="n">
-        <v>42.33</v>
+        <v>31.82</v>
       </c>
       <c r="E37" t="n">
-        <v>34.78</v>
+        <v>0.82</v>
       </c>
       <c r="F37" t="n">
-        <v>-7.150000000000004</v>
+        <v>-30.805</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9124,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1025565261207153</v>
+        <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -9156,10 +9088,10 @@
         <v>39.34</v>
       </c>
       <c r="E38" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="F38" t="n">
-        <v>-15.135</v>
+        <v>-15.2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9174,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00346609278197116</v>
+        <v>0.003578113586559533</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -9203,13 +9135,13 @@
         <v>2664</v>
       </c>
       <c r="D39" t="n">
-        <v>22.78</v>
+        <v>22.73</v>
       </c>
       <c r="E39" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="F39" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9224,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01346828247166085</v>
+        <v>0.01358136007629251</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -9253,13 +9185,13 @@
         <v>2664</v>
       </c>
       <c r="D40" t="n">
-        <v>14.04</v>
+        <v>14.05</v>
       </c>
       <c r="E40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.109999999999998</v>
+        <v>-5.150000000000002</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9274,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.08561059651994336</v>
+        <v>0.08601626682989295</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -9303,16 +9235,16 @@
         <v>2664</v>
       </c>
       <c r="D41" t="n">
-        <v>21.68</v>
+        <v>22.345</v>
       </c>
       <c r="E41" t="n">
-        <v>15.08</v>
+        <v>16.34</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.09</v>
+        <v>-5.18</v>
       </c>
       <c r="G41" t="n">
-        <v>3403.5</v>
+        <v>2599</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -9324,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1754104188648108</v>
+        <v>0.2017315034629224</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -9353,32 +9285,32 @@
         <v>400</v>
       </c>
       <c r="D42" t="n">
-        <v>6.77</v>
+        <v>4.890000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>3.92</v>
+        <v>3.22</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.8700000000000001</v>
+        <v>-0.8300000000000001</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>5.552113587156062e-49</v>
+        <v>1.181654871147264e-57</v>
       </c>
       <c r="I42" t="n">
-        <v>1.371461346786596e-48</v>
+        <v>2.439545540433061e-57</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.37634375</v>
+        <v>0.343896875</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -9403,28 +9335,28 @@
         <v>400</v>
       </c>
       <c r="D43" t="n">
-        <v>5.68</v>
+        <v>4.43</v>
       </c>
       <c r="E43" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.7249999999999996</v>
+        <v>-0.7699999999999997</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.821113643886472e-49</v>
+        <v>1.73481007362291e-57</v>
       </c>
       <c r="I43" t="n">
-        <v>1.063266405255366e-48</v>
+        <v>3.17222413462475e-57</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.357740625</v>
+        <v>0.309796875</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -9453,28 +9385,28 @@
         <v>400</v>
       </c>
       <c r="D44" t="n">
-        <v>4.885</v>
+        <v>3.82</v>
       </c>
       <c r="E44" t="n">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.63</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.571561721320545e-49</v>
+        <v>5.359391024560511e-57</v>
       </c>
       <c r="I44" t="n">
-        <v>1.371461346786596e-48</v>
+        <v>9.527806265885352e-57</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.32493125</v>
+        <v>0.300265625</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -9503,37 +9435,37 @@
         <v>400</v>
       </c>
       <c r="D45" t="n">
-        <v>21.15</v>
+        <v>11.11</v>
       </c>
       <c r="E45" t="n">
-        <v>18.59</v>
+        <v>21.32</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.559999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H45" t="n">
-        <v>2.508112404254496e-67</v>
+        <v>3.501592927726071e-67</v>
       </c>
       <c r="I45" t="n">
-        <v>1.333130531022628e-66</v>
+        <v>8.003640977659591e-67</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.355675</v>
+        <v>0.9662875</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -9553,10 +9485,10 @@
         <v>400</v>
       </c>
       <c r="D46" t="n">
-        <v>11.39</v>
+        <v>11.95</v>
       </c>
       <c r="E46" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="F46" t="n">
         <v>-2.52</v>
@@ -9565,16 +9497,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>7.481966671161719e-63</v>
+        <v>1.939615901792861e-67</v>
       </c>
       <c r="I46" t="n">
-        <v>2.998368953258194e-62</v>
+        <v>5.9243243736828e-67</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3565875</v>
+        <v>0.33471875</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -9603,28 +9535,28 @@
         <v>400</v>
       </c>
       <c r="D47" t="n">
-        <v>8.49</v>
+        <v>8.74</v>
       </c>
       <c r="E47" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.72</v>
+        <v>-1.88</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7.495922383145484e-63</v>
+        <v>1.943918935114669e-67</v>
       </c>
       <c r="I47" t="n">
-        <v>2.998368953258194e-62</v>
+        <v>5.9243243736828e-67</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0.39510625</v>
+        <v>0.3792125</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -9653,28 +9585,28 @@
         <v>400</v>
       </c>
       <c r="D48" t="n">
-        <v>8.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.65</v>
+        <v>-1.7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>7.495432274927977e-63</v>
+        <v>1.943809011806541e-67</v>
       </c>
       <c r="I48" t="n">
-        <v>2.998368953258194e-62</v>
+        <v>5.9243243736828e-67</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.400425</v>
+        <v>0.3874125</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -9703,28 +9635,28 @@
         <v>400</v>
       </c>
       <c r="D49" t="n">
-        <v>6.075</v>
+        <v>5.785</v>
       </c>
       <c r="E49" t="n">
-        <v>4.67</v>
+        <v>4.32</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.707921391139714e-67</v>
+        <v>2.689109776691231e-67</v>
       </c>
       <c r="I49" t="n">
-        <v>1.333130531022628e-66</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3917125</v>
+        <v>0.3908375</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -9756,10 +9688,10 @@
         <v>33.98</v>
       </c>
       <c r="E50" t="n">
-        <v>18.45</v>
+        <v>18.49</v>
       </c>
       <c r="F50" t="n">
-        <v>-15.53</v>
+        <v>-14.39</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -9768,7 +9700,7 @@
         <v>3.652951953368755e-69</v>
       </c>
       <c r="I50" t="n">
-        <v>2.125353863778185e-68</v>
+        <v>1.461180781347502e-68</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
@@ -9803,44 +9735,40 @@
         <v>400</v>
       </c>
       <c r="D51" t="n">
-        <v>7.56</v>
+        <v>30.14</v>
       </c>
       <c r="E51" t="n">
-        <v>7.56</v>
+        <v>20.33</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-7.410000000000002</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>4.088011052551927e-69</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.49035076720418e-68</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>0.33300625</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9857,44 +9785,40 @@
         <v>400</v>
       </c>
       <c r="D52" t="n">
-        <v>2.53</v>
+        <v>16.37</v>
       </c>
       <c r="E52" t="n">
-        <v>2.53</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-6.66</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>4.191611532761757e-69</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.49035076720418e-68</v>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5</v>
+        <v>0.22519375</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9911,44 +9835,40 @@
         <v>400</v>
       </c>
       <c r="D53" t="n">
-        <v>6.72</v>
+        <v>10.745</v>
       </c>
       <c r="E53" t="n">
-        <v>6.72</v>
+        <v>0.03</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-10.71</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2.71597542349433e-67</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9965,44 +9885,40 @@
         <v>400</v>
       </c>
       <c r="D54" t="n">
-        <v>2.005</v>
+        <v>33.44</v>
       </c>
       <c r="E54" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-19.78</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2.727457768070496e-67</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10019,44 +9935,40 @@
         <v>400</v>
       </c>
       <c r="D55" t="n">
-        <v>2.4</v>
+        <v>31.395</v>
       </c>
       <c r="E55" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-16.995</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2.728235197751723e-67</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10073,44 +9985,40 @@
         <v>400</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>29.015</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-15.29</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>2.729377744142024e-67</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10127,32 +10035,32 @@
         <v>400</v>
       </c>
       <c r="D57" t="n">
-        <v>0.28</v>
+        <v>6.72</v>
       </c>
       <c r="E57" t="n">
-        <v>0.28</v>
+        <v>1.44</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-5.149999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0006549583433856954</v>
+        <v>2.600985781330149e-67</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0008383466795336901</v>
+        <v>6.469636134262577e-67</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0.49861875</v>
+        <v>0</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -10177,7 +10085,7 @@
         <v>416</v>
       </c>
       <c r="D58" t="n">
-        <v>7.55</v>
+        <v>7.62</v>
       </c>
       <c r="E58" t="n">
         <v>3.78</v>
@@ -10189,16 +10097,16 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1.694166265164362e-57</v>
+        <v>1.706153553714375e-57</v>
       </c>
       <c r="I58" t="n">
-        <v>5.421332048525959e-57</v>
+        <v>3.17222413462475e-57</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0.252785225591716</v>
+        <v>0.2554635493713018</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -10227,7 +10135,7 @@
         <v>416</v>
       </c>
       <c r="D59" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="E59" t="n">
         <v>2.84</v>
@@ -10239,16 +10147,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.664563639558388e-57</v>
+        <v>1.6616858012641e-57</v>
       </c>
       <c r="I59" t="n">
-        <v>5.421332048525959e-57</v>
+        <v>3.17222413462475e-57</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2450882951183432</v>
+        <v>0.2526003143491125</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -10277,7 +10185,7 @@
         <v>416</v>
       </c>
       <c r="D60" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="E60" t="n">
         <v>2.27</v>
@@ -10289,16 +10197,16 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.343779035469139e-57</v>
+        <v>1.282408677000754e-57</v>
       </c>
       <c r="I60" t="n">
-        <v>4.777881015001385e-57</v>
+        <v>2.564817354001508e-57</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2509447808801775</v>
+        <v>0.2593755778476332</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -10327,44 +10235,40 @@
         <v>416</v>
       </c>
       <c r="D61" t="n">
-        <v>20.49</v>
+        <v>26.25</v>
       </c>
       <c r="E61" t="n">
-        <v>20.49</v>
+        <v>14.14</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-12.11</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>4.179042464136149e-72</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.431442888224668e-71</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>0.009615384615384616</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10381,44 +10285,40 @@
         <v>416</v>
       </c>
       <c r="D62" t="n">
-        <v>5.57</v>
+        <v>11.41</v>
       </c>
       <c r="E62" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10435,44 +10335,40 @@
         <v>416</v>
       </c>
       <c r="D63" t="n">
-        <v>3.65</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>-1.239999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10489,44 +10385,40 @@
         <v>416</v>
       </c>
       <c r="D64" t="n">
-        <v>3.21</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-1.239999999999999</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.077885401036853e-70</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>0.3035606971153846</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10543,44 +10435,40 @@
         <v>416</v>
       </c>
       <c r="D65" t="n">
-        <v>2.58</v>
+        <v>5.42</v>
       </c>
       <c r="E65" t="n">
-        <v>2.58</v>
+        <v>4.69</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-0.7900000000000005</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3.029989884439326e-71</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.292795684027446e-70</v>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>0.2995735484467456</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
